--- a/Reports/FIO/CertificateOfTheDeceased/CertificateOfTheDeceased.xlsx
+++ b/Reports/FIO/CertificateOfTheDeceased/CertificateOfTheDeceased.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\FIO\CertificateOfTheDeceased\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C854EE67-3754-491C-AB82-73FB600EC0DB}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C3B172-97C0-4FA8-AEFD-528EAA750731}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="120" windowWidth="13665" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,10 +90,10 @@
     <t>"постоянно  проживал (был зарегистрирован) в ".$this-&gt;H['pref_region']." " .$this-&gt;H['name_region']. "по адресу:"</t>
   </si>
   <si>
-    <t>Информация не является исчерпывающей, в связи с всиуплением в силу приказа МВД России</t>
-  </si>
-  <si>
     <t>№984 от  31.12.2017 г.</t>
+  </si>
+  <si>
+    <t>Информация не является исчерпывающей, в связи с вступлением в силу приказа МВД России</t>
   </si>
 </sst>
 </file>
@@ -841,7 +841,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="6"/>
@@ -852,7 +852,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
